--- a/results/Int All Data -0.4/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.4/Rando_4_permute.xlsx
@@ -440,1087 +440,1087 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8987623132841118</v>
+        <v>0.9013122781710858</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8987623132841118</v>
+        <v>0.9002953290185435</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8978634198189306</v>
+        <v>0.902211171636267</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8979224476626113</v>
+        <v>0.902211171636267</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8954163266080817</v>
+        <v>0.9032281207888093</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8956524379828041</v>
+        <v>0.90328714863249</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8972292975496803</v>
+        <v>0.9042450699413518</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.900251485186099</v>
+        <v>0.9037441873706986</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.900251485186099</v>
+        <v>0.900737183745516</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9016512612219333</v>
+        <v>0.8998382902803348</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8999276861464878</v>
+        <v>0.9008552394328772</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8995600432744321</v>
+        <v>0.90250631085467</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8959492854024712</v>
+        <v>0.8954601704405262</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8949323362499289</v>
+        <v>0.8951802152333592</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8959931292349157</v>
+        <v>0.8928950215423159</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8948429403837759</v>
+        <v>0.8943251656006226</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8952257672670678</v>
+        <v>0.8940452103934557</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8941059464384004</v>
+        <v>0.8952830869094843</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8932508968056636</v>
+        <v>0.8952830869094843</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8933099246493443</v>
+        <v>0.8959020251674986</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8962123483971378</v>
+        <v>0.8985835215518059</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8931935771632471</v>
+        <v>0.9034473399510315</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8902759694042173</v>
+        <v>0.9034473399510315</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8910129633495929</v>
+        <v>0.9032854404312259</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8903788410803424</v>
+        <v>0.9034473399510315</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.888963881033272</v>
+        <v>0.9089587564294798</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8792734450623494</v>
+        <v>0.9061136523241027</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8790221496763908</v>
+        <v>0.9061136523241027</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8825283276709625</v>
+        <v>0.9061136523241027</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8828673107218099</v>
+        <v>0.9031066486989201</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8821303167764345</v>
+        <v>0.9020896995463776</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8736574487065121</v>
+        <v>0.9018097443392108</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8830189610340311</v>
+        <v>0.9032247043862812</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8725139028602882</v>
+        <v>0.9013240457797939</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8730738132746219</v>
+        <v>0.9077799077571317</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8796308387268207</v>
+        <v>0.8998956099227513</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8822836752899197</v>
+        <v>0.8988044489152922</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8792328278322926</v>
+        <v>0.8997033423804733</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8792328278322926</v>
+        <v>0.896047032474804</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8802480687835709</v>
+        <v>0.8911866304781065</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.8815871087744604</v>
+        <v>0.8905086643764116</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8815871087744604</v>
+        <v>0.893780439197525</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8877326475221592</v>
+        <v>0.867764913546036</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8886619090098127</v>
+        <v>0.867086947444341</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8910347903657448</v>
+        <v>0.8625334522747548</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8889249720044793</v>
+        <v>0.8624153965873935</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8876432516560062</v>
+        <v>0.8558145273027502</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8823662383510164</v>
+        <v>0.8577960407690701</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8833831875035587</v>
+        <v>0.8532880976331922</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8781803860534857</v>
+        <v>0.8498830831134815</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8690177842731603</v>
+        <v>0.8554518192343462</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8683550021827016</v>
+        <v>0.8610070795452389</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8708020953935506</v>
+        <v>0.8613308785848501</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8642264695275874</v>
+        <v>0.8627458386319207</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8701089452806194</v>
+        <v>0.863865659460588</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8666010590847837</v>
+        <v>0.8292269440279385</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8666010590847837</v>
+        <v>0.8201334294987379</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.86682198644827</v>
+        <v>0.8200726934537932</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8669400421356313</v>
+        <v>0.8239347467117126</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8492252358266745</v>
+        <v>0.8176459088579726</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8505221401863837</v>
+        <v>0.8088913773796192</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8394672310057509</v>
+        <v>0.8086114221724524</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8394672310057509</v>
+        <v>0.80681363524209</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8402042249511265</v>
+        <v>0.7959105661738189</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8457156414295747</v>
+        <v>0.7862858010514928</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8356338375690398</v>
+        <v>0.7821589765976427</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8337179949513163</v>
+        <v>0.7757351908440413</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8463042116651167</v>
+        <v>0.7697953954485925</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8436075312695732</v>
+        <v>0.7680127925294664</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8459821208267694</v>
+        <v>0.7680718203731471</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8459821208267694</v>
+        <v>0.7717567901000246</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.833588171655247</v>
+        <v>0.7100567502419952</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8247307685007688</v>
+        <v>0.7112946267580238</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8281931026628959</v>
+        <v>0.7121344923795243</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.807719171712187</v>
+        <v>0.6925560384914685</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8039026704879761</v>
+        <v>0.6894343955814528</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6761903315808453</v>
+        <v>0.6717144646687039</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5731495435306622</v>
+        <v>0.6778381764002506</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5366270617040256</v>
+        <v>0.6771163664661113</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.532839220301023</v>
+        <v>0.6461442101467154</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5424336174008768</v>
+        <v>0.6033867937062274</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5400607360449446</v>
+        <v>0.6029449389792548</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5398398086814584</v>
+        <v>0.587864368819633</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5391466585685273</v>
+        <v>0.583944995919297</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5384686924668324</v>
+        <v>0.5937941048076376</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5302150435591322</v>
+        <v>0.5862284814090762</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5259263195854764</v>
+        <v>0.5555683565205838</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5236563099056692</v>
+        <v>0.5552293734697363</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5236563099056692</v>
+        <v>0.5630529352591721</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.5231992711674607</v>
+        <v>0.5566257331030425</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5228602881166132</v>
+        <v>0.5380052005238484</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5344447396891074</v>
+        <v>0.5393155806935297</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5367147493689146</v>
+        <v>0.5264594681800064</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5372898437944844</v>
+        <v>0.5345157249416365</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5355662687190388</v>
+        <v>0.5472942091977148</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5329572759883843</v>
+        <v>0.5441101220414903</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5478000265720196</v>
+        <v>0.5441101220414903</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5438502856492113</v>
+        <v>0.5480160191318542</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5381600774384573</v>
+        <v>0.5519826522671627</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5274306754986998</v>
+        <v>0.5969072067113329</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5279905859130336</v>
+        <v>0.6061087175204509</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5313956004327443</v>
+        <v>0.5885355021162716</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5313956004327443</v>
+        <v>0.5885355021162716</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5313956004327443</v>
+        <v>0.5942257103270256</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5307614781634938</v>
+        <v>0.5921007079545239</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5105236585875074</v>
+        <v>0.5848539487919221</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5043629358285725</v>
+        <v>0.5797608518230304</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.504023952777725</v>
+        <v>0.5790238578776549</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5056598401882817</v>
+        <v>0.5621827016151992</v>
       </c>
     </row>
     <row r="111">
@@ -1530,353 +1530,353 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5053798849811149</v>
+        <v>0.5650143299106042</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5053798849811149</v>
+        <v>0.5399244595441001</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5005346669956535</v>
+        <v>0.5089674872359405</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4866263025034639</v>
+        <v>0.510279575606886</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.50137282441589</v>
+        <v>0.5064478903714389</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.4995446694630554</v>
+        <v>0.5058289521134245</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4995446694630554</v>
+        <v>0.5058289521134245</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5002226355647503</v>
+        <v>0.4937335585628333</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5002226355647503</v>
+        <v>0.4933355476683052</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4988228595289161</v>
+        <v>0.4904769677529561</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5003845350845559</v>
+        <v>0.4904769677529561</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.500487406760681</v>
+        <v>0.4900351130259837</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.5006341222692505</v>
+        <v>0.486156167555564</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5006341222692505</v>
+        <v>0.4858762123483972</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.500973105320098</v>
+        <v>0.4906673372938296</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5005312505931254</v>
+        <v>0.4906673372938296</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5005750944255699</v>
+        <v>0.4916252586026914</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.501075976996223</v>
+        <v>0.4916252586026914</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.501075976996223</v>
+        <v>0.4926573917664699</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5006779661016949</v>
+        <v>0.4812551483288098</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4984973522880407</v>
+        <v>0.4672860477916754</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4984973522880407</v>
+        <v>0.4583982766147247</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4984973522880407</v>
+        <v>0.4903046292254257</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4993372179095412</v>
+        <v>0.5008687152428493</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.4974365593030539</v>
+        <v>0.5008838992540855</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4982764249245544</v>
+        <v>0.5053024465238104</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4996171731167081</v>
+        <v>0.5059804126255053</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5102201681629244</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5</v>
+        <v>0.5082318218915481</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5</v>
+        <v>0.5044726403097538</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5</v>
+        <v>0.4970975762522064</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5</v>
+        <v>0.4973185036156927</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5</v>
+        <v>0.4976574866665401</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.5</v>
+        <v>0.4987182796515269</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5</v>
+        <v>0.4976136428340957</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,11 +1896,11 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5</v>
+        <v>0.4997200447928332</v>
       </c>
     </row>
     <row r="149">
@@ -1910,43 +1910,43 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5</v>
+        <v>0.4997200447928332</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5</v>
+        <v>0.4997200447928332</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5</v>
+        <v>0.4997200447928332</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5</v>
+        <v>0.4997200447928332</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B156" t="n">
